--- a/data/Poids-Masse grasse.xlsx
+++ b/data/Poids-Masse grasse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24133D12-6A68-F949-AC84-F1E4C043E7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A82E185-AB6E-8E49-88FF-F488BDE41019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
+    <workbookView xWindow="18760" yWindow="500" windowWidth="10000" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="36">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -142,6 +142,9 @@
   <si>
     <t xml:space="preserve">Mehdi Boussaid </t>
   </si>
+  <si>
+    <t>Ryad</t>
+  </si>
 </sst>
 </file>
 
@@ -232,7 +235,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="63">
     <dxf>
       <fill>
         <patternFill>
@@ -447,6 +450,56 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="1"/>
         </patternFill>
       </fill>
@@ -457,6 +510,16 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="4" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
@@ -472,6 +535,33 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="0"/>
       </font>
@@ -482,6 +572,23 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="0"/>
       </font>
@@ -497,7 +604,27 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -508,63 +635,6 @@
       <fill>
         <patternFill>
           <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1099,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E12607-389A-2244-B566-4C295327EA86}">
-  <dimension ref="A1:D241"/>
+  <dimension ref="A1:E268"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -4375,31 +4445,324 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A242" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B242" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A243" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B243" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A244" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B244" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C244">
+        <v>76.8</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A245" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B245" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C245">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A246" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B246" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C246">
+        <v>85.3</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A247" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B247" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C247">
+        <v>87.4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A248" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B248" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A249" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B249" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C249">
+        <v>62.4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A250" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B250" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C250">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A251" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B251" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C251">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A252" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B252" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A253" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B253" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C253">
+        <v>65.2</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A254" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B254" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A255" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B255" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C255">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A256" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B256" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A257" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B257" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A258" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B258" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C258">
+        <v>67.400000000000006</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A259" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B259" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A260" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B260" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A261" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B261" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C261">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A262" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B262" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A263" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B263" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C263">
+        <v>87.7</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A264" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B264" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C264">
+        <v>78.8</v>
+      </c>
+      <c r="E264">
+        <v>77.099999999999994</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A265" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B265" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C265">
+        <v>77.7</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A266" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B266" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C266">
+        <v>78.8</v>
+      </c>
+      <c r="E266">
+        <v>77.099999999999994</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A267" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B267" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C267">
+        <v>66.900000000000006</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A268" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C268">
+        <v>77.7</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A21:A26 A232:A239 A241">
-    <cfRule type="cellIs" dxfId="55" priority="70" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="77" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="69" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="76" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="68" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="75" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="67" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="74" operator="equal">
       <formula>"RENFO/TEK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="73" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="72" operator="equal">
       <formula>"B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="71" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:A52">
+    <cfRule type="cellIs" dxfId="55" priority="63" operator="equal">
+      <formula>"NN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="54" priority="62" operator="equal">
+      <formula>"NN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="53" priority="61" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="60" operator="equal">
+      <formula>"RENFO/TEK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="59" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="50" priority="58" operator="equal">
+      <formula>"B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="57" operator="equal">
+      <formula>"R"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A72:A79">
     <cfRule type="cellIs" dxfId="48" priority="56" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
@@ -4422,7 +4785,7 @@
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A72:A79">
+  <conditionalFormatting sqref="A99:A105">
     <cfRule type="cellIs" dxfId="41" priority="49" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
@@ -4445,9 +4808,9 @@
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A99:A105">
-    <cfRule type="cellIs" dxfId="34" priority="36" operator="equal">
-      <formula>"R"</formula>
+  <conditionalFormatting sqref="A124:A132">
+    <cfRule type="cellIs" dxfId="34" priority="39" operator="equal">
+      <formula>"RENFO/TEK"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="33" priority="37" operator="equal">
       <formula>"B"</formula>
@@ -4455,8 +4818,8 @@
     <cfRule type="cellIs" dxfId="32" priority="38" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="39" operator="equal">
-      <formula>"RENFO/TEK"</formula>
+    <cfRule type="cellIs" dxfId="31" priority="36" operator="equal">
+      <formula>"R"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="30" priority="40" operator="equal">
       <formula>"OK"</formula>
@@ -4468,30 +4831,30 @@
       <formula>"NN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A124:A132">
-    <cfRule type="cellIs" dxfId="27" priority="30" operator="equal">
+  <conditionalFormatting sqref="A151:A159">
+    <cfRule type="cellIs" dxfId="27" priority="35" operator="equal">
+      <formula>"NN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="34" operator="equal">
+      <formula>"NN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="33" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="32" operator="equal">
+      <formula>"RENFO/TEK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="31" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="30" operator="equal">
       <formula>"B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="31" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="32" operator="equal">
-      <formula>"RENFO/TEK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="33" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="34" operator="equal">
-      <formula>"NN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="35" operator="equal">
-      <formula>"NN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="21" priority="29" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A151:A159">
+  <conditionalFormatting sqref="A178:A186">
     <cfRule type="cellIs" dxfId="20" priority="24" operator="equal">
       <formula>"P"</formula>
     </cfRule>
@@ -4514,7 +4877,7 @@
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A178:A186">
+  <conditionalFormatting sqref="A205:A214">
     <cfRule type="cellIs" dxfId="13" priority="21" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
@@ -4537,26 +4900,26 @@
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A205:A214">
-    <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
+  <conditionalFormatting sqref="A258:A265 A267:A268">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"RENFO/TEK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/Poids-Masse grasse.xlsx
+++ b/data/Poids-Masse grasse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A82E185-AB6E-8E49-88FF-F488BDE41019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A433B1A1-7493-9541-8086-0144ECD262DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18760" yWindow="500" windowWidth="10000" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
@@ -4098,9 +4098,6 @@
       <c r="B216" s="1">
         <v>46056</v>
       </c>
-      <c r="C216">
-        <v>79.400000000000006</v>
-      </c>
       <c r="D216" s="7">
         <v>8.1000000000000003E-2</v>
       </c>
@@ -4452,6 +4449,9 @@
       <c r="B242" s="1">
         <v>46084</v>
       </c>
+      <c r="C242">
+        <v>77.5</v>
+      </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A243" s="4" t="s">
@@ -4460,6 +4460,9 @@
       <c r="B243" s="1">
         <v>46084</v>
       </c>
+      <c r="C243">
+        <v>92.8</v>
+      </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244" s="4" t="s">
@@ -4512,6 +4515,9 @@
       <c r="B248" s="1">
         <v>46084</v>
       </c>
+      <c r="C248">
+        <v>77.7</v>
+      </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249" s="4" t="s">
@@ -4591,6 +4597,9 @@
       <c r="B256" s="1">
         <v>46084</v>
       </c>
+      <c r="C256">
+        <v>75</v>
+      </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" s="4" t="s">
@@ -4599,6 +4608,9 @@
       <c r="B257" s="1">
         <v>46084</v>
       </c>
+      <c r="C257">
+        <v>78.7</v>
+      </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" s="5" t="s">
@@ -4618,6 +4630,9 @@
       <c r="B259" s="1">
         <v>46084</v>
       </c>
+      <c r="C259">
+        <v>87.7</v>
+      </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" s="4" t="s">
@@ -4644,6 +4659,9 @@
       </c>
       <c r="B262" s="1">
         <v>46084</v>
+      </c>
+      <c r="C262">
+        <v>75.2</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">

--- a/data/Poids-Masse grasse.xlsx
+++ b/data/Poids-Masse grasse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A433B1A1-7493-9541-8086-0144ECD262DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1652029E-32CB-394E-B6AB-B65E08583A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18760" yWindow="500" windowWidth="10000" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -202,7 +202,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -229,6 +229,9 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1169,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E12607-389A-2244-B566-4C295327EA86}">
-  <dimension ref="A1:E268"/>
+  <dimension ref="A1:D268"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -4452,6 +4455,9 @@
       <c r="C242">
         <v>77.5</v>
       </c>
+      <c r="D242" s="6">
+        <v>7.1999999999999995E-2</v>
+      </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A243" s="4" t="s">
@@ -4463,6 +4469,9 @@
       <c r="C243">
         <v>92.8</v>
       </c>
+      <c r="D243" s="6">
+        <v>0.112</v>
+      </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244" s="4" t="s">
@@ -4474,6 +4483,9 @@
       <c r="C244">
         <v>76.8</v>
       </c>
+      <c r="D244" s="6">
+        <v>5.0999999999999997E-2</v>
+      </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245" s="4" t="s">
@@ -4485,6 +4497,9 @@
       <c r="C245">
         <v>79</v>
       </c>
+      <c r="D245" s="6">
+        <v>4.1000000000000002E-2</v>
+      </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A246" s="4" t="s">
@@ -4496,6 +4511,9 @@
       <c r="C246">
         <v>85.3</v>
       </c>
+      <c r="D246" s="6">
+        <v>6.5000000000000002E-2</v>
+      </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
@@ -4507,6 +4525,9 @@
       <c r="C247">
         <v>87.4</v>
       </c>
+      <c r="D247" s="6">
+        <v>7.8E-2</v>
+      </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
@@ -4518,6 +4539,9 @@
       <c r="C248">
         <v>77.7</v>
       </c>
+      <c r="D248" s="6">
+        <v>8.3000000000000004E-2</v>
+      </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249" s="4" t="s">
@@ -4529,6 +4553,9 @@
       <c r="C249">
         <v>62.4</v>
       </c>
+      <c r="D249" s="6">
+        <v>3.6999999999999998E-2</v>
+      </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A250" s="4" t="s">
@@ -4540,6 +4567,9 @@
       <c r="C250">
         <v>71.8</v>
       </c>
+      <c r="D250" s="6">
+        <v>6.2E-2</v>
+      </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A251" s="4" t="s">
@@ -4551,6 +4581,9 @@
       <c r="C251">
         <v>79.8</v>
       </c>
+      <c r="D251" s="6">
+        <v>8.7999999999999995E-2</v>
+      </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252" s="4" t="s">
@@ -4559,6 +4592,7 @@
       <c r="B252" s="1">
         <v>46084</v>
       </c>
+      <c r="D252" s="6"/>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A253" s="4" t="s">
@@ -4570,6 +4604,9 @@
       <c r="C253">
         <v>65.2</v>
       </c>
+      <c r="D253" s="6">
+        <v>6.5000000000000002E-2</v>
+      </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A254" s="4" t="s">
@@ -4578,6 +4615,7 @@
       <c r="B254" s="1">
         <v>46084</v>
       </c>
+      <c r="D254" s="6"/>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
@@ -4589,6 +4627,9 @@
       <c r="C255">
         <v>76.3</v>
       </c>
+      <c r="D255" s="6">
+        <v>7.1999999999999995E-2</v>
+      </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
@@ -4600,8 +4641,11 @@
       <c r="C256">
         <v>75</v>
       </c>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D256" s="6">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A257" s="4" t="s">
         <v>22</v>
       </c>
@@ -4611,8 +4655,11 @@
       <c r="C257">
         <v>78.7</v>
       </c>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D257" s="6">
+        <v>8.5999999999999993E-2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A258" s="5" t="s">
         <v>23</v>
       </c>
@@ -4622,8 +4669,11 @@
       <c r="C258">
         <v>67.400000000000006</v>
       </c>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D258" s="6">
+        <v>8.1000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A259" s="4" t="s">
         <v>25</v>
       </c>
@@ -4633,16 +4683,20 @@
       <c r="C259">
         <v>87.7</v>
       </c>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D259" s="6">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A260" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B260" s="1">
         <v>46084</v>
       </c>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D260" s="6"/>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A261" s="4" t="s">
         <v>27</v>
       </c>
@@ -4652,8 +4706,11 @@
       <c r="C261">
         <v>71</v>
       </c>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D261" s="6">
+        <v>8.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A262" s="4" t="s">
         <v>28</v>
       </c>
@@ -4663,8 +4720,11 @@
       <c r="C262">
         <v>75.2</v>
       </c>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D262" s="6">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A263" s="4" t="s">
         <v>30</v>
       </c>
@@ -4674,8 +4734,11 @@
       <c r="C263">
         <v>87.7</v>
       </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D263" s="6">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
         <v>31</v>
       </c>
@@ -4685,11 +4748,11 @@
       <c r="C264">
         <v>78.8</v>
       </c>
-      <c r="E264">
-        <v>77.099999999999994</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D264" s="6">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A265" s="4" t="s">
         <v>32</v>
       </c>
@@ -4699,8 +4762,11 @@
       <c r="C265">
         <v>77.7</v>
       </c>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D265" s="6">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A266" s="4" t="s">
         <v>34</v>
       </c>
@@ -4710,11 +4776,11 @@
       <c r="C266">
         <v>78.8</v>
       </c>
-      <c r="E266">
-        <v>77.099999999999994</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D266" s="6">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A267" s="4" t="s">
         <v>33</v>
       </c>
@@ -4724,13 +4790,19 @@
       <c r="C267">
         <v>66.900000000000006</v>
       </c>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D267" s="6">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A268" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C268">
         <v>77.7</v>
+      </c>
+      <c r="D268" s="11">
+        <v>8.1000000000000003E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/Poids-Masse grasse.xlsx
+++ b/data/Poids-Masse grasse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1652029E-32CB-394E-B6AB-B65E08583A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE29FD05-CE20-D343-B09E-D531B2E95BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="36">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">Mehdi Boussaid </t>
   </si>
   <si>
-    <t>Ryad</t>
+    <t>Ryad Kralladi</t>
   </si>
 </sst>
 </file>
@@ -202,7 +202,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -230,15 +230,79 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="70">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1172,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E12607-389A-2244-B566-4C295327EA86}">
-  <dimension ref="A1:D268"/>
+  <dimension ref="A1:D295"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -4798,38 +4862,307 @@
       <c r="A268" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="B268" s="1">
+        <v>46084</v>
+      </c>
       <c r="C268">
         <v>77.7</v>
       </c>
-      <c r="D268" s="11">
+      <c r="D268" s="7">
         <v>8.1000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A269" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B269" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C269">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A270" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B270" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A271" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B271" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A272" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B272" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C272">
+        <v>77.8</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A273" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B273" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A274" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B274" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C274">
+        <v>88.6</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A275" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B275" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A276" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B276" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A277" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B277" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A278" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B278" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A279" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B279" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A280" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B280" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A281" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B281" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A282" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B282" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A283" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B283" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A284" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B284" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A285" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B285" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A286" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B286" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C286">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A287" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B287" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A288" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B288" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C288">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A289" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B289" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A290" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B290" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C290">
+        <v>88.2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A291" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B291" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A292" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B292" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A293" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B293" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C293">
+        <v>78.599999999999994</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A294" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B294" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C294">
+        <v>67.7</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A295" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B295" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C295">
+        <v>75.3</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A21:A26 A232:A239 A241">
-    <cfRule type="cellIs" dxfId="62" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="84" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="83" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="75" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="82" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="74" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="81" operator="equal">
       <formula>"RENFO/TEK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="73" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="80" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="79" operator="equal">
       <formula>"B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="78" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:A52">
+    <cfRule type="cellIs" dxfId="62" priority="70" operator="equal">
+      <formula>"NN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="69" operator="equal">
+      <formula>"NN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="68" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="59" priority="67" operator="equal">
+      <formula>"RENFO/TEK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="58" priority="66" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="65" operator="equal">
+      <formula>"B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="56" priority="64" operator="equal">
+      <formula>"R"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A72:A79">
     <cfRule type="cellIs" dxfId="55" priority="63" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
@@ -4852,7 +5185,7 @@
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A72:A79">
+  <conditionalFormatting sqref="A99:A105">
     <cfRule type="cellIs" dxfId="48" priority="56" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
@@ -4875,55 +5208,55 @@
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A99:A105">
-    <cfRule type="cellIs" dxfId="41" priority="49" operator="equal">
+  <conditionalFormatting sqref="A124:A132">
+    <cfRule type="cellIs" dxfId="41" priority="46" operator="equal">
+      <formula>"RENFO/TEK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="44" operator="equal">
+      <formula>"B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="45" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="43" operator="equal">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="47" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="48" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="48" operator="equal">
-      <formula>"NN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="47" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="46" operator="equal">
-      <formula>"RENFO/TEK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="45" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="44" operator="equal">
-      <formula>"B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="43" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A124:A132">
-    <cfRule type="cellIs" dxfId="34" priority="39" operator="equal">
-      <formula>"RENFO/TEK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="37" operator="equal">
-      <formula>"B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="38" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="36" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="40" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="41" operator="equal">
-      <formula>"NN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="49" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A151:A159">
-    <cfRule type="cellIs" dxfId="27" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="42" operator="equal">
       <formula>"NN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="41" operator="equal">
+      <formula>"NN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="40" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="39" operator="equal">
+      <formula>"RENFO/TEK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="38" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="37" operator="equal">
+      <formula>"B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="36" operator="equal">
+      <formula>"R"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A178:A186">
+    <cfRule type="cellIs" dxfId="27" priority="31" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="26" priority="34" operator="equal">
       <formula>"NN"</formula>
@@ -4934,8 +5267,8 @@
     <cfRule type="cellIs" dxfId="24" priority="32" operator="equal">
       <formula>"RENFO/TEK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="31" operator="equal">
-      <formula>"P"</formula>
+    <cfRule type="cellIs" dxfId="23" priority="35" operator="equal">
+      <formula>"NN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="22" priority="30" operator="equal">
       <formula>"B"</formula>
@@ -4944,9 +5277,9 @@
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A178:A186">
-    <cfRule type="cellIs" dxfId="20" priority="24" operator="equal">
-      <formula>"P"</formula>
+  <conditionalFormatting sqref="A205:A214">
+    <cfRule type="cellIs" dxfId="20" priority="28" operator="equal">
+      <formula>"NN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="19" priority="27" operator="equal">
       <formula>"NN"</formula>
@@ -4957,8 +5290,8 @@
     <cfRule type="cellIs" dxfId="17" priority="25" operator="equal">
       <formula>"RENFO/TEK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="28" operator="equal">
-      <formula>"NN"</formula>
+    <cfRule type="cellIs" dxfId="16" priority="24" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="15" priority="23" operator="equal">
       <formula>"B"</formula>
@@ -4967,50 +5300,50 @@
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A205:A214">
-    <cfRule type="cellIs" dxfId="13" priority="21" operator="equal">
+  <conditionalFormatting sqref="A258:A265 A267:A268">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
       <formula>"RENFO/TEK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A258:A265 A267:A268">
+  <conditionalFormatting sqref="A285:A292 A294:A295">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"RENFO/TEK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"NN"</formula>
+    </cfRule>
     <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>"NN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"NN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"RENFO/TEK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Poids-Masse grasse.xlsx
+++ b/data/Poids-Masse grasse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE29FD05-CE20-D343-B09E-D531B2E95BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED5293E-6829-1140-859D-63F9C4390F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
@@ -460,11 +460,88 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="1"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="0"/>
       </font>
@@ -480,6 +557,46 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -490,7 +607,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
+          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -505,136 +622,19 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4944,6 +4944,9 @@
       <c r="B276" s="1">
         <v>46119</v>
       </c>
+      <c r="C276">
+        <v>63.7</v>
+      </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4" t="s">
@@ -4960,6 +4963,9 @@
       <c r="B278" s="1">
         <v>46119</v>
       </c>
+      <c r="C278">
+        <v>80</v>
+      </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A279" s="4" t="s">
@@ -4992,6 +4998,9 @@
       <c r="B282" s="1">
         <v>46119</v>
       </c>
+      <c r="C282">
+        <v>77.099999999999994</v>
+      </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A283" s="4" t="s">
@@ -4999,6 +5008,9 @@
       </c>
       <c r="B283" s="1">
         <v>46119</v>
+      </c>
+      <c r="C283">
+        <v>73.7</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.2">
@@ -5209,8 +5221,8 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A124:A132">
-    <cfRule type="cellIs" dxfId="41" priority="46" operator="equal">
-      <formula>"RENFO/TEK"</formula>
+    <cfRule type="cellIs" dxfId="41" priority="43" operator="equal">
+      <formula>"R"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="40" priority="44" operator="equal">
       <formula>"B"</formula>
@@ -5218,8 +5230,8 @@
     <cfRule type="cellIs" dxfId="39" priority="45" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="43" operator="equal">
-      <formula>"R"</formula>
+    <cfRule type="cellIs" dxfId="38" priority="46" operator="equal">
+      <formula>"RENFO/TEK"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="37" priority="47" operator="equal">
       <formula>"OK"</formula>
@@ -5232,31 +5244,31 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A151:A159">
-    <cfRule type="cellIs" dxfId="34" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="37" operator="equal">
+      <formula>"B"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="38" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="39" operator="equal">
+      <formula>"RENFO/TEK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="40" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="41" operator="equal">
       <formula>"NN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="42" operator="equal">
       <formula>"NN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="40" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="39" operator="equal">
-      <formula>"RENFO/TEK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="38" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="37" operator="equal">
-      <formula>"B"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="28" priority="36" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A178:A186">
-    <cfRule type="cellIs" dxfId="27" priority="31" operator="equal">
-      <formula>"P"</formula>
+    <cfRule type="cellIs" dxfId="27" priority="35" operator="equal">
+      <formula>"NN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="26" priority="34" operator="equal">
       <formula>"NN"</formula>
@@ -5267,8 +5279,8 @@
     <cfRule type="cellIs" dxfId="24" priority="32" operator="equal">
       <formula>"RENFO/TEK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="35" operator="equal">
-      <formula>"NN"</formula>
+    <cfRule type="cellIs" dxfId="23" priority="31" operator="equal">
+      <formula>"P"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="22" priority="30" operator="equal">
       <formula>"B"</formula>
@@ -5324,26 +5336,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A285:A292 A294:A295">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"NN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"NN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"RENFO/TEK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"B"</formula>
+    </cfRule>
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"B"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"P"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"RENFO/TEK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"NN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>"NN"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Poids-Masse grasse.xlsx
+++ b/data/Poids-Masse grasse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED5293E-6829-1140-859D-63F9C4390F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD167E6-3B73-6349-9F0A-AAC6E8C09865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{6E33DD24-57FC-B141-A642-57CD5D231636}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -4882,6 +4882,9 @@
       <c r="C269">
         <v>78.8</v>
       </c>
+      <c r="D269" s="7">
+        <v>7.1999999999999995E-2</v>
+      </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A270" s="4" t="s">
@@ -4890,6 +4893,7 @@
       <c r="B270" s="1">
         <v>46119</v>
       </c>
+      <c r="D270" s="7"/>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A271" s="4" t="s">
@@ -4898,6 +4902,12 @@
       <c r="B271" s="1">
         <v>46119</v>
       </c>
+      <c r="C271">
+        <v>76.599999999999994</v>
+      </c>
+      <c r="D271" s="7">
+        <v>5.5E-2</v>
+      </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A272" s="4" t="s">
@@ -4909,16 +4919,25 @@
       <c r="C272">
         <v>77.8</v>
       </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D272" s="7">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B273" s="1">
         <v>46119</v>
       </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C273">
+        <v>87.1</v>
+      </c>
+      <c r="D273" s="7">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A274" s="4" t="s">
         <v>9</v>
       </c>
@@ -4928,16 +4947,20 @@
       <c r="C274">
         <v>88.6</v>
       </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D274" s="7">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A275" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B275" s="1">
         <v>46119</v>
       </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D275" s="7"/>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
         <v>11</v>
       </c>
@@ -4947,16 +4970,20 @@
       <c r="C276">
         <v>63.7</v>
       </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D276" s="7">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A277" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B277" s="1">
         <v>46119</v>
       </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D277" s="7"/>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A278" s="4" t="s">
         <v>13</v>
       </c>
@@ -4966,32 +4993,43 @@
       <c r="C278">
         <v>80</v>
       </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D278" s="7">
+        <v>8.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A279" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B279" s="1">
         <v>46119</v>
       </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D279" s="7"/>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A280" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B280" s="1">
         <v>46119</v>
       </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D280" s="7"/>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A281" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B281" s="1">
         <v>46119</v>
       </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C281">
+        <v>65.7</v>
+      </c>
+      <c r="D281" s="7">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A282" s="4" t="s">
         <v>20</v>
       </c>
@@ -5001,8 +5039,11 @@
       <c r="C282">
         <v>77.099999999999994</v>
       </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D282" s="7">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A283" s="4" t="s">
         <v>21</v>
       </c>
@@ -5012,24 +5053,29 @@
       <c r="C283">
         <v>73.7</v>
       </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D283" s="7">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A284" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B284" s="1">
         <v>46119</v>
       </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D284" s="7"/>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A285" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B285" s="1">
         <v>46119</v>
       </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D285" s="7"/>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
         <v>25</v>
       </c>
@@ -5039,16 +5085,20 @@
       <c r="C286">
         <v>87.5</v>
       </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D286" s="7">
+        <v>8.1000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A287" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B287" s="1">
         <v>46119</v>
       </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D287" s="7"/>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A288" s="4" t="s">
         <v>27</v>
       </c>
@@ -5058,16 +5108,20 @@
       <c r="C288">
         <v>69.8</v>
       </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D288" s="7">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A289" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B289" s="1">
         <v>46119</v>
       </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D289" s="7"/>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A290" s="4" t="s">
         <v>30</v>
       </c>
@@ -5077,24 +5131,29 @@
       <c r="C290">
         <v>88.2</v>
       </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D290" s="7">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A291" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B291" s="1">
         <v>46119</v>
       </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D291" s="7"/>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A292" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B292" s="1">
         <v>46119</v>
       </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D292" s="7"/>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
         <v>34</v>
       </c>
@@ -5104,8 +5163,11 @@
       <c r="C293">
         <v>78.599999999999994</v>
       </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D293" s="7">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A294" s="4" t="s">
         <v>33</v>
       </c>
@@ -5115,8 +5177,11 @@
       <c r="C294">
         <v>67.7</v>
       </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D294" s="7">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A295" s="4" t="s">
         <v>35</v>
       </c>
@@ -5125,6 +5190,9 @@
       </c>
       <c r="C295">
         <v>75.3</v>
+      </c>
+      <c r="D295" s="7">
+        <v>6.9000000000000006E-2</v>
       </c>
     </row>
   </sheetData>
